--- a/data/test_output/att.xlsx
+++ b/data/test_output/att.xlsx
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/test_output/att.xlsx
+++ b/data/test_output/att.xlsx
@@ -443,7 +443,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
